--- a/data/trans_orig/P1405-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2012</t>
+          <t>Población con diagnóstico de colitis en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448230</t>
+          <t>449250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420531</t>
+          <t>420494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429255</t>
+          <t>429257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874599</t>
+          <t>873024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883384</t>
+          <t>882435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26477</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>672418</t>
+          <t>671178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684363</t>
+          <t>684255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>591563</t>
+          <t>592427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606353</t>
+          <t>606406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270865</t>
+          <t>1270550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1288673</t>
+          <t>1288289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>677336</t>
+          <t>676701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698044</t>
+          <t>698303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>708599</t>
+          <t>708575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1378261</t>
+          <t>1379355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1389509</t>
+          <t>1389485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602898</t>
+          <t>602875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612591</t>
+          <t>612526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591274</t>
+          <t>590777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607870</t>
+          <t>607105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1200551</t>
+          <t>1200285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1219286</t>
+          <t>1218348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418572</t>
+          <t>418737</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428368</t>
+          <t>428352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428004</t>
+          <t>426930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442675</t>
+          <t>441774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851760</t>
+          <t>851319</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>868822</t>
+          <t>869021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13420</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19626</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296366</t>
+          <t>295766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308703</t>
+          <t>307836</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>343448</t>
+          <t>342396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>353015</t>
+          <t>352984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>644156</t>
+          <t>644890</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>659778</t>
+          <t>659162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26840</t>
+          <t>26356</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236616</t>
+          <t>236473</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247752</t>
+          <t>248688</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>360956</t>
+          <t>361440</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377704</t>
+          <t>377947</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>604444</t>
+          <t>605399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>624570</t>
+          <t>623547</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>42327</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>46485</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80268</t>
+          <t>79684</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73653</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113629</t>
+          <t>110948</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3384694</t>
+          <t>3384452</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3407653</t>
+          <t>3407844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3473648</t>
+          <t>3474232</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3506092</t>
+          <t>3507431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6867065</t>
+          <t>6869746</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6907041</t>
+          <t>6909442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2016</t>
+          <t>Población con diagnóstico de colitis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411930</t>
+          <t>411029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387651</t>
+          <t>387670</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394761</t>
+          <t>394763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>802533</t>
+          <t>803403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813138</t>
+          <t>813192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581567</t>
+          <t>582670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589567</t>
+          <t>590496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>554758</t>
+          <t>554123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562602</t>
+          <t>562568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1140416</t>
+          <t>1140524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151127</t>
+          <t>1151138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>25591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655100</t>
+          <t>655119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667001</t>
+          <t>666434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644243</t>
+          <t>643697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656775</t>
+          <t>656552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305245</t>
+          <t>1304892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320930</t>
+          <t>1320831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631241</t>
+          <t>631456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642990</t>
+          <t>643519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632993</t>
+          <t>633177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645939</t>
+          <t>645814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270395</t>
+          <t>1270320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1287118</t>
+          <t>1286779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>465207</t>
+          <t>464936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476777</t>
+          <t>476775</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474681</t>
+          <t>472797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489159</t>
+          <t>488737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>943892</t>
+          <t>944185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963533</t>
+          <t>964690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>332361</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>334330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>367885</t>
+          <t>367743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>376743</t>
+          <t>376784</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>701996</t>
+          <t>702895</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>711059</t>
+          <t>711108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>24701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>26420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249837</t>
+          <t>249684</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>376559</t>
+          <t>375468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>393911</t>
+          <t>393081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>630554</t>
+          <t>630747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>648844</t>
+          <t>648649</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40427</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41414</t>
+          <t>41740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72720</t>
+          <t>73977</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,47 +6161,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>81136</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>62648</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>100946</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>81136</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>64884</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>99993</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3353923</t>
+          <t>3356676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3378114</t>
+          <t>3378612</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3471822</t>
+          <t>3470565</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3503128</t>
+          <t>3502802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,47 +6274,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6496</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6857756</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6837946</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6876244</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>98,83%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6496</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6857756</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6838899</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6874008</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1405-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Edad-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449250</t>
+          <t>448743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420494</t>
+          <t>420518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429257</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>873024</t>
+          <t>873619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>882435</t>
+          <t>882439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>671178</t>
+          <t>671684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684255</t>
+          <t>684340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>592427</t>
+          <t>592601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606406</t>
+          <t>606377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270550</t>
+          <t>1271080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1288289</t>
+          <t>1287910</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676701</t>
+          <t>673223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698303</t>
+          <t>698440</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>708575</t>
+          <t>708576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1379355</t>
+          <t>1379383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1389485</t>
+          <t>1389511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>24315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>29447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602875</t>
+          <t>602993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612526</t>
+          <t>612495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>590777</t>
+          <t>589949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607105</t>
+          <t>607031</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1200285</t>
+          <t>1199433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218348</t>
+          <t>1218255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418737</t>
+          <t>419748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428352</t>
+          <t>428367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>426930</t>
+          <t>428885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>441774</t>
+          <t>442681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851319</t>
+          <t>852838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869021</t>
+          <t>869050</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295766</t>
+          <t>296585</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307836</t>
+          <t>308708</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342396</t>
+          <t>342661</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>352984</t>
+          <t>353012</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>644890</t>
+          <t>644827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>659162</t>
+          <t>659696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>34369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236473</t>
+          <t>235692</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248688</t>
+          <t>248725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>361440</t>
+          <t>361468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377947</t>
+          <t>378282</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>605399</t>
+          <t>603278</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>623547</t>
+          <t>623307</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42327</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46485</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79684</t>
+          <t>81547</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,47 +3182,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>91495</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>72854</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>113983</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>91495</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>71252</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>110948</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3384452</t>
+          <t>3384464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3407844</t>
+          <t>3407972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3474232</t>
+          <t>3472369</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3507431</t>
+          <t>3506221</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,47 +3295,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6423</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6889199</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6866711</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6907840</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6423</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6889199</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6869746</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6909442</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411029</t>
+          <t>410904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387670</t>
+          <t>386778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394763</t>
+          <t>394762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803403</t>
+          <t>802448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813192</t>
+          <t>813225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>582670</t>
+          <t>582501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>589570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>554123</t>
+          <t>554078</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562568</t>
+          <t>562597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1140524</t>
+          <t>1140349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151138</t>
+          <t>1151113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655119</t>
+          <t>654175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666434</t>
+          <t>666366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643697</t>
+          <t>644939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656552</t>
+          <t>656691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1304892</t>
+          <t>1304804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320831</t>
+          <t>1321065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631456</t>
+          <t>632283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643519</t>
+          <t>642976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633177</t>
+          <t>633352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645814</t>
+          <t>645842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270320</t>
+          <t>1271160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286779</t>
+          <t>1286941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>29312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>464936</t>
+          <t>465260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476775</t>
+          <t>476784</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472797</t>
+          <t>473243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>488737</t>
+          <t>488996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>944185</t>
+          <t>945455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>964690</t>
+          <t>963770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>367743</t>
+          <t>367665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>376784</t>
+          <t>376781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>702895</t>
+          <t>702129</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>711108</t>
+          <t>711095</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26420</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249684</t>
+          <t>249875</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>375468</t>
+          <t>376479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>393081</t>
+          <t>393782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>630747</t>
+          <t>630640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>648649</t>
+          <t>649648</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41740</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73977</t>
+          <t>73727</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62648</t>
+          <t>65212</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100946</t>
+          <t>102598</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3356676</t>
+          <t>3356509</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3378612</t>
+          <t>3377888</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3470565</t>
+          <t>3470815</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3502802</t>
+          <t>3502527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6837946</t>
+          <t>6836294</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6876244</t>
+          <t>6873680</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
